--- a/frontend/public/templates/範例旅程.xlsx
+++ b/frontend/public/templates/範例旅程.xlsx
@@ -1756,7 +1756,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="10" width="24" customWidth="1" style="0"/>
+    <col min="1" max="11" width="24" customWidth="1" style="0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1797,15 +1797,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">航廈</t>
+          <t xml:space="preserve">出發航廈</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">抵達航廈</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">行李說明</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">備註</t>
         </is>
@@ -1849,22 +1854,27 @@
       </c>
       <c r="H2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">T1</t>
         </is>
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">T2</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">請依實際訂票資訊填寫</t>
         </is>
       </c>
-      <c r="J2" s="0" t="inlineStr">
+      <c r="K2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">此航班僅供功能示範</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1001"/>
+  <autoFilter ref="A1:K1001"/>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="ID 格式錯誤" error="請使用 A001 至 A9999 格式" sqref="A2:A1001">
       <formula1>OR(A2="",IFERROR(AND(EXACT(A2,"A"&amp;TEXT(VALUE(MID(A2,2,4)),"000")),VALUE(MID(A2,2,4))&gt;=1,VALUE(MID(A2,2,4))&lt;=9999),FALSE))</formula1>
@@ -1876,7 +1886,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="8" width="24" customWidth="1" style="0"/>
+    <col min="1" max="11" width="24" customWidth="1" style="0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1892,30 +1902,45 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">飯店圖片網址</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">入住日期</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入住時間</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">退房日期</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">退房時間</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">地址</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">地圖網址</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">電話</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">備註</t>
         </is>
@@ -1934,37 +1959,52 @@
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-01</t>
         </is>
       </c>
-      <c r="D2" s="0" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-05-03</t>
         </is>
       </c>
-      <c r="E2" s="0" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">日本大阪（範例地址）</t>
         </is>
       </c>
-      <c r="F2" s="0" t="inlineStr">
+      <c r="I2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.google.com/maps/search/?api=1&amp;query=Osaka</t>
         </is>
       </c>
-      <c r="G2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H2" s="0" t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">到店費用由公積金支付</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1001"/>
+  <autoFilter ref="A1:K1001"/>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="ID 格式錯誤" error="請使用 H001 至 H9999 格式" sqref="A2:A1001">
       <formula1>OR(A2="",IFERROR(AND(EXACT(A2,"H"&amp;TEXT(VALUE(MID(A2,2,4)),"000")),VALUE(MID(A2,2,4))&gt;=1,VALUE(MID(A2,2,4))&lt;=9999),FALSE))</formula1>

--- a/frontend/public/templates/範例旅程.xlsx
+++ b/frontend/public/templates/範例旅程.xlsx
@@ -491,12 +491,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:M1001"/>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="ID 格式錯誤" error="請使用 I001 至 I9999 格式" sqref="A2:A1001">
       <formula1>OR(A2="",IFERROR(AND(EXACT(A2,"I"&amp;TEXT(VALUE(MID(A2,2,4)),"000")),VALUE(MID(A2,2,4))&gt;=1,VALUE(MID(A2,2,4))&lt;=9999),FALSE))</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="請選擇固定選項" error="請使用下拉選單" sqref="G2:G1001">
-      <formula1>"景點,餐飲,交通,住宿,自由活動,其他"</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="ID 格式錯誤" error="請使用 A001 至 A9999 格式" sqref="K2:K1001">
       <formula1>OR(K2="",IFERROR(AND(EXACT(K2,"A"&amp;TEXT(VALUE(MID(K2,2,4)),"000")),VALUE(MID(K2,2,4))&gt;=1,VALUE(MID(K2,2,4))&lt;=9999),FALSE))</formula1>
@@ -1886,7 +1883,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="11" width="24" customWidth="1" style="0"/>
+    <col min="1" max="13" width="24" customWidth="1" style="0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1945,6 +1942,16 @@
           <t xml:space="preserve">備註</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">訂房網站網址</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">價格</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -2002,9 +2009,19 @@
           <t xml:space="preserve">到店費用由公積金支付</t>
         </is>
       </c>
+      <c r="L2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1001"/>
+  <autoFilter ref="A1:M1001"/>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="ID 格式錯誤" error="請使用 H001 至 H9999 格式" sqref="A2:A1001">
       <formula1>OR(A2="",IFERROR(AND(EXACT(A2,"H"&amp;TEXT(VALUE(MID(A2,2,4)),"000")),VALUE(MID(A2,2,4))&gt;=1,VALUE(MID(A2,2,4))&lt;=9999),FALSE))</formula1>

--- a/frontend/public/templates/範例旅程.xlsx
+++ b/frontend/public/templates/範例旅程.xlsx
@@ -1883,7 +1883,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="13" width="24" customWidth="1" style="0"/>
+    <col min="1" max="14" width="24" customWidth="1" style="0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1952,6 +1952,11 @@
           <t xml:space="preserve">價格</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">副標題</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -2019,9 +2024,14 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="N2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1001"/>
+  <autoFilter ref="A1:N1001"/>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="ID 格式錯誤" error="請使用 H001 至 H9999 格式" sqref="A2:A1001">
       <formula1>OR(A2="",IFERROR(AND(EXACT(A2,"H"&amp;TEXT(VALUE(MID(A2,2,4)),"000")),VALUE(MID(A2,2,4))&gt;=1,VALUE(MID(A2,2,4))&lt;=9999),FALSE))</formula1>

--- a/frontend/public/templates/範例旅程.xlsx
+++ b/frontend/public/templates/範例旅程.xlsx
@@ -151,7 +151,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="13" width="24" customWidth="1" style="0"/>
+    <col min="1" max="14" width="24" customWidth="1" style="0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -220,6 +220,11 @@
           <t xml:space="preserve">排序</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">內文</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -287,6 +292,11 @@
           <t xml:space="preserve">10</t>
         </is>
       </c>
+      <c r="N2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -354,6 +364,11 @@
           <t xml:space="preserve">20</t>
         </is>
       </c>
+      <c r="N3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
@@ -421,6 +436,11 @@
           <t xml:space="preserve">10</t>
         </is>
       </c>
+      <c r="N4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
@@ -488,9 +508,14 @@
           <t xml:space="preserve">10</t>
         </is>
       </c>
+      <c r="N5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1001"/>
+  <autoFilter ref="A1:N1001"/>
   <dataValidations count="3">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="ID 格式錯誤" error="請使用 I001 至 I9999 格式" sqref="A2:A1001">
       <formula1>OR(A2="",IFERROR(AND(EXACT(A2,"I"&amp;TEXT(VALUE(MID(A2,2,4)),"000")),VALUE(MID(A2,2,4))&gt;=1,VALUE(MID(A2,2,4))&lt;=9999),FALSE))</formula1>

--- a/frontend/public/templates/範例旅程.xlsx
+++ b/frontend/public/templates/範例旅程.xlsx
@@ -151,7 +151,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="14" width="24" customWidth="1" style="0"/>
+    <col min="1" max="15" width="24" customWidth="1" style="0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -225,6 +225,11 @@
           <t xml:space="preserve">內文</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">類別</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -297,6 +302,11 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="O2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">交通</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -369,6 +379,11 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="O3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未分類</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
@@ -441,6 +456,11 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="O4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">活動</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
@@ -513,10 +533,15 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="O5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">活動</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1001"/>
-  <dataValidations count="3">
+  <autoFilter ref="A1:O1001"/>
+  <dataValidations count="4">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="ID 格式錯誤" error="請使用 I001 至 I9999 格式" sqref="A2:A1001">
       <formula1>OR(A2="",IFERROR(AND(EXACT(A2,"I"&amp;TEXT(VALUE(MID(A2,2,4)),"000")),VALUE(MID(A2,2,4))&gt;=1,VALUE(MID(A2,2,4))&lt;=9999),FALSE))</formula1>
     </dataValidation>
@@ -525,6 +550,9 @@
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="ID 格式錯誤" error="請使用 H001 至 H9999 格式" sqref="L2:L1001">
       <formula1>OR(L2="",IFERROR(AND(EXACT(L2,"H"&amp;TEXT(VALUE(MID(L2,2,4)),"000")),VALUE(MID(L2,2,4))&gt;=1,VALUE(MID(L2,2,4))&lt;=9999),FALSE))</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="請選擇固定選項" error="請使用下拉選單" sqref="O2:O1001">
+      <formula1>"未分類,三餐,活動,交通,購物"</formula1>
     </dataValidation>
   </dataValidations>
 </worksheet>
